--- a/Website Structure-Change pipeline.xlsx
+++ b/Website Structure-Change pipeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PS\Documents\Coding\kalki\dashboard-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4E6592-FC59-48B0-9F4C-28B2B7E23241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FF0FE3-3FC6-4467-8EBA-DA61883E91D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">Page to track portfolio performance </t>
   </si>
@@ -52,14 +52,46 @@
   </si>
   <si>
     <t xml:space="preserve">Change main business line to clothing wholesale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show indicator for pointer moves on page and clicks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">List of websites for considerations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add more text and content related to ethnic wear, indian fashion, clothing styles and trading income via wheel strategy and </t>
+  </si>
+  <si>
+    <t>https://www.soch.com/intl/</t>
+  </si>
+  <si>
+    <t>suta.in</t>
+  </si>
+  <si>
+    <t>indyvogue.com</t>
+  </si>
+  <si>
+    <t>sacredweaves.com</t>
+  </si>
+  <si>
+    <t>tulsisilks.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -87,8 +119,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -369,10 +402,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I15"/>
+  <dimension ref="B1:R21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>8</v>
       </c>
@@ -380,42 +413,77 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="R5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="R6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="R7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="R8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="R9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="R10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>